--- a/地图表格/level3.xlsx
+++ b/地图表格/level3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\52724\SIMGame\SIMGame\地图表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AA802F8-E76B-4B1C-83EA-AB35162CFA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7902D944-D583-473D-B785-4FD2EC2EACB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>箱子</t>
   </si>
@@ -41,44 +41,61 @@
     <t>尖刺</t>
   </si>
   <si>
-    <t>钥匙</t>
-  </si>
-  <si>
-    <t>踩住</t>
-  </si>
-  <si>
-    <t>机关</t>
-  </si>
-  <si>
-    <t>可移动</t>
-  </si>
-  <si>
     <t>光线</t>
   </si>
   <si>
+    <t>出生地</t>
+  </si>
+  <si>
     <t>出口</t>
-  </si>
-  <si>
-    <t>出生地</t>
-  </si>
-  <si>
-    <t>机关门</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>机关门（障碍）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>压力机关</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>光敏开关</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>隐藏光敏平台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>光敏开关2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钥匙4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机关门4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机关锁5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机关门5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可动砖块3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可动砖块1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可动砖块1·</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐藏门2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>砖块机关1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>砖块机关3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可动砖块3·</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -123,7 +140,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -174,13 +191,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF33D3D"/>
+        <fgColor rgb="FF164F10"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -199,35 +228,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -239,35 +253,44 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,8 +565,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AX62"/>
+  <sheetFormatPr defaultColWidth="5.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="31:50" x14ac:dyDescent="0.25">
       <c r="AX1" s="1"/>
@@ -649,7 +672,7 @@
       <c r="AF15" s="1"/>
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
-      <c r="AI15" s="2" t="s">
+      <c r="AI15" s="13" t="s">
         <v>0</v>
       </c>
       <c r="AJ15" s="1"/>
@@ -673,10 +696,12 @@
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
-      <c r="AI16" s="14" t="s">
+      <c r="AI16" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="AJ16" s="1"/>
+      <c r="AJ16" s="20" t="s">
+        <v>16</v>
+      </c>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
@@ -711,11 +736,11 @@
       <c r="AX22" s="1"/>
     </row>
     <row r="23" spans="33:50" x14ac:dyDescent="0.25">
-      <c r="AR23" s="4" t="s">
+      <c r="AR23" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="AT23" s="5" t="s">
-        <v>2</v>
+      <c r="AT23" s="14" t="s">
+        <v>6</v>
       </c>
       <c r="AX23" s="1"/>
     </row>
@@ -757,11 +782,11 @@
       <c r="AX31" s="1"/>
     </row>
     <row r="32" spans="33:50" x14ac:dyDescent="0.25">
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI32" s="6" t="s">
-        <v>4</v>
+      <c r="AG32" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI32" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="AX32" s="1"/>
     </row>
@@ -842,60 +867,60 @@
     <row r="36" spans="1:50" x14ac:dyDescent="0.25">
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
-      <c r="AQ36" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="AQ36" s="1"/>
       <c r="AX36" s="1"/>
     </row>
     <row r="37" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="N37" s="16"/>
-      <c r="O37" s="10"/>
+      <c r="N37" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="O37" s="5"/>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
-      <c r="AQ37" s="12" t="s">
+      <c r="AQ37" s="17" t="s">
         <v>9</v>
       </c>
       <c r="AX37" s="1"/>
     </row>
     <row r="38" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
+      <c r="A38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
       <c r="N38" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="18" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>5</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
-      <c r="AQ38" s="11"/>
+      <c r="AQ38" s="18"/>
       <c r="AX38" s="1"/>
     </row>
     <row r="39" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="N39" s="17"/>
+      <c r="N39" s="8"/>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
-      <c r="AQ39" s="11"/>
+      <c r="AQ39" s="18"/>
       <c r="AX39" s="1"/>
     </row>
     <row r="40" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="L40" s="13" t="s">
-        <v>11</v>
+      <c r="L40" s="19" t="s">
+        <v>14</v>
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
@@ -907,15 +932,15 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
-      <c r="O41" s="20" t="s">
+      <c r="O41" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="10"/>
+      <c r="P41" s="12"/>
+      <c r="Q41" s="12"/>
+      <c r="R41" s="12"/>
+      <c r="S41" s="12"/>
+      <c r="T41" s="12"/>
+      <c r="U41" s="5"/>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
       <c r="AC41" s="1"/>
@@ -970,8 +995,8 @@
     </row>
     <row r="43" spans="1:50" x14ac:dyDescent="0.25">
       <c r="K43" s="1"/>
-      <c r="O43" s="7"/>
-      <c r="P43" s="7"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
       <c r="AC43" s="1"/>
@@ -998,20 +1023,20 @@
       <c r="AX43" s="1"/>
     </row>
     <row r="44" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="13" t="s">
         <v>0</v>
       </c>
       <c r="K44" s="1"/>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
-      <c r="AV44" s="1"/>
+      <c r="AU44" s="1"/>
       <c r="AX44" s="1"/>
     </row>
     <row r="45" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="C45" s="1"/>
+      <c r="C45" s="5"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -1022,48 +1047,50 @@
       <c r="K45" s="1"/>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
-      <c r="AV45" s="1"/>
+      <c r="AU45" s="1"/>
       <c r="AX45" s="1"/>
     </row>
     <row r="46" spans="1:50" x14ac:dyDescent="0.25">
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
-      <c r="AV46" s="1"/>
+      <c r="AU46" s="1"/>
       <c r="AX46" s="1"/>
     </row>
     <row r="47" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
-      <c r="AV47" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="AW47" s="9" t="s">
+      <c r="AU47" s="11" t="s">
         <v>7</v>
       </c>
+      <c r="AW47" s="5"/>
       <c r="AX47" s="1"/>
     </row>
     <row r="48" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="W48" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="X48" s="11"/>
+      <c r="W48" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="6"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AV48" s="21"/>
-      <c r="AW48" s="9"/>
+      <c r="AU48" s="10"/>
+      <c r="AV48" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW48" s="6"/>
       <c r="AX48" s="1"/>
     </row>
     <row r="49" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="P49" s="10"/>
-      <c r="W49" s="11"/>
-      <c r="X49" s="11"/>
+      <c r="P49" s="5"/>
+      <c r="W49" s="6"/>
+      <c r="X49" s="6"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AV49" s="21"/>
-      <c r="AW49" s="9"/>
+      <c r="AU49" s="10"/>
+      <c r="AV49" s="6"/>
+      <c r="AW49" s="6"/>
       <c r="AX49" s="1"/>
     </row>
     <row r="50" spans="1:50" x14ac:dyDescent="0.25">
@@ -1118,12 +1145,14 @@
       <c r="AW50" s="1"/>
       <c r="AX50" s="1"/>
     </row>
+    <row r="62" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="W48:X49"/>
     <mergeCell ref="AQ37:AQ39"/>
-    <mergeCell ref="O41:Q41"/>
-    <mergeCell ref="AV47:AV49"/>
+    <mergeCell ref="AU47:AU49"/>
+    <mergeCell ref="AV48:AW49"/>
+    <mergeCell ref="O41:T41"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/地图表格/level3.xlsx
+++ b/地图表格/level3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\52724\SIMGame\SIMGame\地图表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7902D944-D583-473D-B785-4FD2EC2EACB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221764D3-A33E-435E-8549-355834311EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>箱子</t>
   </si>
@@ -41,61 +41,66 @@
     <t>尖刺</t>
   </si>
   <si>
+    <t>出生地</t>
+  </si>
+  <si>
+    <t>出口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>光敏开关2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钥匙4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机关门4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机关锁5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机关门5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可动砖块3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可动砖块1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可动砖块1·</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐藏门2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>砖块机关1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>砖块机关3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可动砖块3·</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>光源→</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>光线</t>
-  </si>
-  <si>
-    <t>出生地</t>
-  </si>
-  <si>
-    <t>出口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>光敏开关2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>钥匙4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>机关门4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>机关锁5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>机关门5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>可动砖块3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>可动砖块1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>可动砖块1·</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>隐藏门2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>砖块机关1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>砖块机关3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>可动砖块3·</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -115,12 +120,14 @@
       <sz val="11"/>
       <color theme="5" tint="-0.499984740745262"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -228,69 +235,66 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -672,7 +676,7 @@
       <c r="AF15" s="1"/>
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
-      <c r="AI15" s="13" t="s">
+      <c r="AI15" s="5" t="s">
         <v>0</v>
       </c>
       <c r="AJ15" s="1"/>
@@ -696,11 +700,11 @@
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
-      <c r="AI16" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ16" s="20" t="s">
-        <v>16</v>
+      <c r="AI16" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ16" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
@@ -736,11 +740,11 @@
       <c r="AX22" s="1"/>
     </row>
     <row r="23" spans="33:50" x14ac:dyDescent="0.25">
-      <c r="AR23" s="3" t="s">
+      <c r="AR23" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AT23" s="14" t="s">
-        <v>6</v>
+      <c r="AT23" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="AX23" s="1"/>
     </row>
@@ -782,11 +786,11 @@
       <c r="AX31" s="1"/>
     </row>
     <row r="32" spans="33:50" x14ac:dyDescent="0.25">
-      <c r="AG32" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI32" s="16" t="s">
-        <v>8</v>
+      <c r="AG32" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI32" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="AX32" s="1"/>
     </row>
@@ -871,56 +875,56 @@
       <c r="AX36" s="1"/>
     </row>
     <row r="37" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="N37" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="O37" s="5"/>
+      <c r="N37" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
-      <c r="AQ37" s="17" t="s">
-        <v>9</v>
+      <c r="AQ37" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="AX37" s="1"/>
     </row>
     <row r="38" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="O38" s="9" t="s">
-        <v>5</v>
+      <c r="A38" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
-      <c r="AQ38" s="18"/>
+      <c r="AQ38" s="12"/>
       <c r="AX38" s="1"/>
     </row>
     <row r="39" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="N39" s="8"/>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
-      <c r="AQ39" s="18"/>
+      <c r="AQ39" s="12"/>
       <c r="AX39" s="1"/>
     </row>
     <row r="40" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="L40" s="19" t="s">
-        <v>14</v>
+      <c r="L40" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
@@ -932,15 +936,14 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
-      <c r="O41" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="P41" s="12"/>
-      <c r="Q41" s="12"/>
-      <c r="R41" s="12"/>
-      <c r="S41" s="12"/>
-      <c r="T41" s="12"/>
-      <c r="U41" s="5"/>
+      <c r="O41" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="P41" s="16"/>
+      <c r="Q41" s="16"/>
+      <c r="R41" s="16"/>
+      <c r="S41" s="16"/>
+      <c r="T41" s="16"/>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
       <c r="AC41" s="1"/>
@@ -995,8 +998,8 @@
     </row>
     <row r="43" spans="1:50" x14ac:dyDescent="0.25">
       <c r="K43" s="1"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
       <c r="AC43" s="1"/>
@@ -1023,10 +1026,10 @@
       <c r="AX43" s="1"/>
     </row>
     <row r="44" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H44" s="13" t="s">
+      <c r="H44" s="5" t="s">
         <v>0</v>
       </c>
       <c r="K44" s="1"/>
@@ -1036,7 +1039,6 @@
       <c r="AX44" s="1"/>
     </row>
     <row r="45" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="C45" s="5"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -1060,37 +1062,35 @@
       <c r="A47" s="1"/>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
-      <c r="AU47" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="AW47" s="5"/>
+      <c r="AU47" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="AX47" s="1"/>
     </row>
     <row r="48" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="W48" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="X48" s="6"/>
+      <c r="W48" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="X48" s="10"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AU48" s="10"/>
-      <c r="AV48" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW48" s="6"/>
+      <c r="AU48" s="14"/>
+      <c r="AV48" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW48" s="10"/>
       <c r="AX48" s="1"/>
     </row>
     <row r="49" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="P49" s="5"/>
-      <c r="W49" s="6"/>
-      <c r="X49" s="6"/>
+      <c r="W49" s="10"/>
+      <c r="X49" s="10"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AU49" s="10"/>
-      <c r="AV49" s="6"/>
-      <c r="AW49" s="6"/>
+      <c r="AU49" s="14"/>
+      <c r="AV49" s="10"/>
+      <c r="AW49" s="10"/>
       <c r="AX49" s="1"/>
     </row>
     <row r="50" spans="1:50" x14ac:dyDescent="0.25">
@@ -1147,7 +1147,8 @@
     </row>
     <row r="62" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B38:M38"/>
     <mergeCell ref="W48:X49"/>
     <mergeCell ref="AQ37:AQ39"/>
     <mergeCell ref="AU47:AU49"/>
